--- a/purchase_order_request_forms/005_souvenir_booklet_advertising_form--purchase_order_request_forms.xlsx
+++ b/purchase_order_request_forms/005_souvenir_booklet_advertising_form--purchase_order_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>What is your contact name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>choose_souvenir</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>choose_souvenir</t>
+          <t>What is your contact email address?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>make_payment</t>
+          <t>choose_souvenir</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>make_payment</t>
+          <t>What is the size of the souvenir you want to order?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>confirm_contact</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>confirm_details</t>
+          <t>Confirm your contact details?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>confirm_details</t>
+          <t>make_payment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>confirm_details</t>
+          <t>What is your payment method?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>confirm_details</t>
+          <t>confirm_payment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>confirm_details</t>
+          <t>Confirm your payment method?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>confirm_details</t>
+          <t>confirm_address</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>confirm_details</t>
+          <t>Is your address correct?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>confirm_address_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>Confirm your address?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>confirm_payment_details</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>Confirm payment details?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>confirm_confirm_details</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>Confirm confirm details?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>confirm_confirm_details_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>Confirm Confirm Details 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>confirm_address_details_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>Confirm address details?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>confirm_address_details_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>Confirm Address Details 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>confirm_details</t>
+          <t>confirm_details_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>confirm_details</t>
+          <t>Confirm contact details?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>confirm_details</t>
+          <t>confirm_details_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>confirm_details</t>
+          <t>Confirm Details 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>confirm_details</t>
+          <t>confirm_details_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>confirm_details</t>
+          <t>Confirm Details 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>confirm_details</t>
+          <t>confirm_details_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>confirm_details</t>
+          <t>Confirm Details 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>confirm_details</t>
+          <t>confirm_details_5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>confirm_details</t>
+          <t>Confirm Details 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>confirm_details</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>confirm_details</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>confirm_details</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>confirm_details</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>confirm_details</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>confirm_details</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>confirm_details</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>confirm_details</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>confirm_details</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>confirm_details</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>confirm_details</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>confirm_details</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>confirm_details</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>confirm_details</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1136,7 +975,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1153,7 +992,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1170,58 +1009,109 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>contact_details_choices</t>
+          <t>make_payment_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>address_1</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>address_1</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>contact_details_choices</t>
+          <t>make_payment_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>address_2</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>address_2</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>contact_details_choices</t>
+          <t>make_payment_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>debit_card</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Debit Card</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>confirm_address_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>address_1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Address 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>confirm_address_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>address_2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Address 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>confirm_address_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>address_3</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>address_3</t>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Address 3</t>
         </is>
       </c>
     </row>
